--- a/data.xlsx
+++ b/data.xlsx
@@ -1474,9 +1474,6 @@
     <t>姓名</t>
   </si>
   <si>
-    <t>考試編號</t>
-  </si>
-  <si>
     <t>黃安妤</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1490,6 +1487,10 @@
   </si>
   <si>
     <t>李厚靜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>考卷編號</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1587,7 +1588,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1627,6 +1628,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1935,11 +1939,11 @@
       <c r="E1" s="8" t="s">
         <v>483</v>
       </c>
-      <c r="F1" s="12" t="s">
-        <v>484</v>
+      <c r="F1" s="14" t="s">
+        <v>488</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
@@ -7771,7 +7775,7 @@
         <v>10125</v>
       </c>
       <c r="E140" s="11" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F140" s="12">
         <v>3</v>
@@ -23269,7 +23273,7 @@
         <v>10410</v>
       </c>
       <c r="E509" s="11" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F509" s="12">
         <v>1</v>
@@ -42799,7 +42803,7 @@
         <v>11013</v>
       </c>
       <c r="E974" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F974" s="12">
         <v>1</v>
